--- a/research/traditional_assets/database/data/croatia/croatia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07530000000000001</v>
+        <v>0.056745</v>
       </c>
       <c r="E2">
-        <v>-0.124</v>
+        <v>0.0733</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3.44</v>
+        <v>2.483</v>
       </c>
       <c r="L2">
-        <v>0.1266568483063328</v>
+        <v>0.1158115671641791</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>18.73</v>
+        <v>12.88</v>
       </c>
       <c r="V2">
-        <v>0.6627742392073601</v>
+        <v>0.5300411522633746</v>
       </c>
       <c r="W2">
-        <v>0.03844212470734798</v>
+        <v>0.02717381231099405</v>
       </c>
       <c r="X2">
-        <v>0.07097697201836187</v>
+        <v>0.08402131797766341</v>
       </c>
       <c r="Y2">
-        <v>-0.03253484731101389</v>
+        <v>-0.05684750566666936</v>
       </c>
       <c r="Z2">
-        <v>0.2741080890144825</v>
+        <v>0.2198185266827293</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06260960587506885</v>
+        <v>0.07539569589131206</v>
       </c>
       <c r="AC2">
-        <v>-0.06260960587506885</v>
+        <v>-0.07539569589131206</v>
       </c>
       <c r="AD2">
-        <v>15.575</v>
+        <v>16.154</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.575</v>
+        <v>16.154</v>
       </c>
       <c r="AG2">
-        <v>-3.154999999999996</v>
+        <v>3.273999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3553096840424319</v>
+        <v>0.3993177436100263</v>
       </c>
       <c r="AI2">
-        <v>0.1310199789695058</v>
+        <v>0.1739720421306567</v>
       </c>
       <c r="AJ2">
-        <v>-0.1256721768571996</v>
+        <v>0.118735040255313</v>
       </c>
       <c r="AK2">
-        <v>-0.03150431873783011</v>
+        <v>0.04093830494910845</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.161</v>
+        <v>0.115</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1.16</v>
+        <v>0.903</v>
       </c>
       <c r="L3">
-        <v>0.1404358353510896</v>
+        <v>0.1181937172774869</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,55 +749,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>10.7</v>
+        <v>5.94</v>
       </c>
       <c r="V3">
-        <v>2.034220532319392</v>
+        <v>1.1</v>
       </c>
       <c r="W3">
-        <v>0.04603174603174603</v>
+        <v>0.03369402985074627</v>
       </c>
       <c r="X3">
-        <v>0.06012673986551925</v>
+        <v>0.07285903852996345</v>
       </c>
       <c r="Y3">
-        <v>-0.01409499383377322</v>
+        <v>-0.03916500867921718</v>
       </c>
       <c r="Z3">
-        <v>0.4759435321233075</v>
+        <v>0.4665648854961832</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05895681721043881</v>
+        <v>0.07270543582563271</v>
       </c>
       <c r="AC3">
-        <v>-0.05895681721043881</v>
+        <v>-0.07270543582563271</v>
       </c>
       <c r="AD3">
-        <v>0.275</v>
+        <v>0.154</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.275</v>
+        <v>0.154</v>
       </c>
       <c r="AG3">
-        <v>-10.425</v>
+        <v>-5.786</v>
       </c>
       <c r="AH3">
-        <v>0.04968383017163505</v>
+        <v>0.02772776377385668</v>
       </c>
       <c r="AI3">
-        <v>0.01015697137580794</v>
+        <v>0.007349432089338551</v>
       </c>
       <c r="AJ3">
-        <v>2.018393030009681</v>
+        <v>14.98963730569948</v>
       </c>
       <c r="AK3">
-        <v>-0.6366412213740458</v>
+        <v>-0.3853736512588252</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0104</v>
+        <v>-0.00151</v>
       </c>
       <c r="E4">
-        <v>-0.124</v>
+        <v>0.0733</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -841,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="L4">
-        <v>0.1206349206349206</v>
+        <v>0.1144927536231884</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -868,55 +868,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8.029999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="V4">
-        <v>0.3491304347826087</v>
+        <v>0.3671957671957672</v>
       </c>
       <c r="W4">
-        <v>0.03085250338294993</v>
+        <v>0.02065359477124183</v>
       </c>
       <c r="X4">
-        <v>0.08182720417120448</v>
+        <v>0.09518359742536336</v>
       </c>
       <c r="Y4">
-        <v>-0.05097470078825456</v>
+        <v>-0.07453000265412153</v>
       </c>
       <c r="Z4">
-        <v>0.2312492352869203</v>
+        <v>0.1700344997535732</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0662623945396989</v>
+        <v>0.07808595595699143</v>
       </c>
       <c r="AC4">
-        <v>-0.0662623945396989</v>
+        <v>-0.07808595595699143</v>
       </c>
       <c r="AD4">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="AG4">
-        <v>7.270000000000001</v>
+        <v>9.059999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.3994778067885118</v>
+        <v>0.4584527220630373</v>
       </c>
       <c r="AI4">
-        <v>0.1666666666666667</v>
+        <v>0.2225312934631432</v>
       </c>
       <c r="AJ4">
-        <v>0.2401717872481005</v>
+        <v>0.3240343347639485</v>
       </c>
       <c r="AK4">
-        <v>0.08678524531455177</v>
+        <v>0.1394704433497537</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/croatia/croatia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.056745</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0733</v>
+        <v>0.295</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2.483</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>0.1158115671641791</v>
+        <v>0.1556842867487328</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>12.88</v>
+        <v>15.13</v>
       </c>
       <c r="V2">
-        <v>0.5300411522633746</v>
+        <v>0.4901198574667963</v>
       </c>
       <c r="W2">
-        <v>0.02717381231099405</v>
+        <v>0.05346531504671039</v>
       </c>
       <c r="X2">
-        <v>0.08402131797766341</v>
+        <v>0.06779068184025555</v>
       </c>
       <c r="Y2">
-        <v>-0.05684750566666936</v>
+        <v>-0.01432536679354516</v>
       </c>
       <c r="Z2">
-        <v>0.2198185266827293</v>
+        <v>0.3735360147142354</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07539569589131206</v>
+        <v>0.06487781402764876</v>
       </c>
       <c r="AC2">
-        <v>-0.07539569589131206</v>
+        <v>-0.06487781402764876</v>
       </c>
       <c r="AD2">
-        <v>16.154</v>
+        <v>17.875</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16.154</v>
+        <v>17.875</v>
       </c>
       <c r="AG2">
-        <v>3.273999999999999</v>
+        <v>2.745000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.3993177436100263</v>
+        <v>0.3667042773617807</v>
       </c>
       <c r="AI2">
-        <v>0.1739720421306567</v>
+        <v>0.1506214451232357</v>
       </c>
       <c r="AJ2">
-        <v>0.118735040255313</v>
+        <v>0.08165997322623833</v>
       </c>
       <c r="AK2">
-        <v>0.04093830494910845</v>
+        <v>0.02651021295089092</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,7 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.115</v>
+        <v>0.111</v>
+      </c>
+      <c r="E3">
+        <v>0.271</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0.903</v>
+        <v>1.13</v>
       </c>
       <c r="L3">
-        <v>0.1181937172774869</v>
+        <v>0.1199575371549894</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.94</v>
+        <v>6.8</v>
       </c>
       <c r="V3">
-        <v>1.1</v>
+        <v>0.8323133414932681</v>
       </c>
       <c r="W3">
-        <v>0.03369402985074627</v>
+        <v>0.05022222222222222</v>
       </c>
       <c r="X3">
-        <v>0.07285903852996345</v>
+        <v>0.0616608454827909</v>
       </c>
       <c r="Y3">
-        <v>-0.03916500867921718</v>
+        <v>-0.01143862326056868</v>
       </c>
       <c r="Z3">
-        <v>0.4665648854961832</v>
+        <v>0.8424253264174567</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07270543582563271</v>
+        <v>0.06146685836030058</v>
       </c>
       <c r="AC3">
-        <v>-0.07270543582563271</v>
+        <v>-0.06146685836030058</v>
       </c>
       <c r="AD3">
-        <v>0.154</v>
+        <v>0.575</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.154</v>
+        <v>0.575</v>
       </c>
       <c r="AG3">
-        <v>-5.786</v>
+        <v>-6.225</v>
       </c>
       <c r="AH3">
-        <v>0.02772776377385668</v>
+        <v>0.06575185820468839</v>
       </c>
       <c r="AI3">
-        <v>0.007349432089338551</v>
+        <v>0.02131603336422614</v>
       </c>
       <c r="AJ3">
-        <v>14.98963730569948</v>
+        <v>-3.20051413881748</v>
       </c>
       <c r="AK3">
-        <v>-0.3853736512588252</v>
+        <v>-0.308550185873606</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,10 +826,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00151</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="E4">
-        <v>0.0733</v>
+        <v>0.319</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -841,10 +844,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1.58</v>
+        <v>3.17</v>
       </c>
       <c r="L4">
-        <v>0.1144927536231884</v>
+        <v>0.1741758241758242</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -868,55 +871,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.94</v>
+        <v>8.33</v>
       </c>
       <c r="V4">
-        <v>0.3671957671957672</v>
+        <v>0.3669603524229075</v>
       </c>
       <c r="W4">
-        <v>0.02065359477124183</v>
+        <v>0.05670840787119857</v>
       </c>
       <c r="X4">
-        <v>0.09518359742536336</v>
+        <v>0.07392051819772019</v>
       </c>
       <c r="Y4">
-        <v>-0.07453000265412153</v>
+        <v>-0.01721211032652162</v>
       </c>
       <c r="Z4">
-        <v>0.1700344997535732</v>
+        <v>0.289993626513703</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07808595595699143</v>
+        <v>0.06828876969499695</v>
       </c>
       <c r="AC4">
-        <v>-0.07808595595699143</v>
+        <v>-0.06828876969499695</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>17.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>16</v>
+        <v>17.3</v>
       </c>
       <c r="AG4">
-        <v>9.059999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.4584527220630373</v>
+        <v>0.4325</v>
       </c>
       <c r="AI4">
-        <v>0.2225312934631432</v>
+        <v>0.1886586695747001</v>
       </c>
       <c r="AJ4">
-        <v>0.3240343347639485</v>
+        <v>0.2832333438585412</v>
       </c>
       <c r="AK4">
-        <v>0.1394704433497537</v>
+        <v>0.1075926592299388</v>
       </c>
       <c r="AL4">
         <v>0</v>
